--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_15-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_15-10-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66f01e9e5+80021]
-	GetHandleVerifier [0x0x7ff66f01ea40+80112]
-	(No symbol) [0x0x7ff66eda060f]
-	(No symbol) [0x0x7ff66edf8854]
-	(No symbol) [0x0x7ff66edf8b1c]
-	(No symbol) [0x0x7ff66ee4c927]
-	(No symbol) [0x0x7ff66ee2126f]
-	(No symbol) [0x0x7ff66ee4968a]
-	(No symbol) [0x0x7ff66ee21003]
-	(No symbol) [0x0x7ff66ede95d1]
-	(No symbol) [0x0x7ff66edea3f3]
-	GetHandleVerifier [0x0x7ff66f2ddd8d+2960445]
-	GetHandleVerifier [0x0x7ff66f2d804a+2936570]
-	GetHandleVerifier [0x0x7ff66f2f8a87+3070263]
-	GetHandleVerifier [0x0x7ff66f0384ce+185214]
-	GetHandleVerifier [0x0x7ff66f03ff1f+216527]
-	GetHandleVerifier [0x0x7ff66f027c24+117460]
-	GetHandleVerifier [0x0x7ff66f027ddf+117903]
-	GetHandleVerifier [0x0x7ff66f00dcb8+11112]
+	GetHandleVerifier [0x0x7ff75e9be9e5+80021]
+	GetHandleVerifier [0x0x7ff75e9bea40+80112]
+	(No symbol) [0x0x7ff75e74060f]
+	(No symbol) [0x0x7ff75e798854]
+	(No symbol) [0x0x7ff75e798b1c]
+	(No symbol) [0x0x7ff75e7ec927]
+	(No symbol) [0x0x7ff75e7c126f]
+	(No symbol) [0x0x7ff75e7e968a]
+	(No symbol) [0x0x7ff75e7c1003]
+	(No symbol) [0x0x7ff75e7895d1]
+	(No symbol) [0x0x7ff75e78a3f3]
+	GetHandleVerifier [0x0x7ff75ec7dd8d+2960445]
+	GetHandleVerifier [0x0x7ff75ec7804a+2936570]
+	GetHandleVerifier [0x0x7ff75ec98a87+3070263]
+	GetHandleVerifier [0x0x7ff75e9d84ce+185214]
+	GetHandleVerifier [0x0x7ff75e9dff1f+216527]
+	GetHandleVerifier [0x0x7ff75e9c7c24+117460]
+	GetHandleVerifier [0x0x7ff75e9c7ddf+117903]
+	GetHandleVerifier [0x0x7ff75e9adcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
